--- a/Test upload format/Mudra/IA/2026 - 2027- SHG/Q1 25-26 SHG.xlsx
+++ b/Test upload format/Mudra/IA/2026 - 2027- SHG/Q1 25-26 SHG.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AK$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AK$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1431,7 +1431,7 @@
     <col min="5" max="5" width="7.14285714285714" style="5" customWidth="1"/>
     <col min="6" max="6" width="20.5714285714286" style="5" customWidth="1"/>
     <col min="7" max="7" width="8.57142857142857" style="5" customWidth="1"/>
-    <col min="8" max="8" width="7.85714285714286" style="5" customWidth="1"/>
+    <col min="8" max="8" width="12.2857142857143" style="5" customWidth="1"/>
     <col min="9" max="9" width="8.14285714285714" style="5" customWidth="1"/>
     <col min="10" max="10" width="14.8571428571429" style="5" customWidth="1"/>
     <col min="11" max="11" width="9" style="5" customWidth="1"/>
@@ -1442,11 +1442,11 @@
     <col min="16" max="16" width="20.4285714285714" style="5" customWidth="1"/>
     <col min="17" max="17" width="18.5714285714286" style="5" customWidth="1"/>
     <col min="18" max="18" width="16.8571428571429" style="5" customWidth="1"/>
-    <col min="19" max="19" width="16.1428571428571" style="1" customWidth="1"/>
+    <col min="19" max="19" width="19.4285714285714" style="1" customWidth="1"/>
     <col min="20" max="20" width="11.5714285714286" style="5" customWidth="1"/>
     <col min="21" max="21" width="13.8571428571429" style="1" customWidth="1"/>
     <col min="22" max="22" width="14.8571428571429" style="5" customWidth="1"/>
-    <col min="23" max="23" width="9.42857142857143" style="5" customWidth="1"/>
+    <col min="23" max="23" width="14.1428571428571" style="5" customWidth="1"/>
     <col min="24" max="24" width="15" style="1" customWidth="1"/>
     <col min="25" max="25" width="8.57142857142857" style="5" customWidth="1"/>
     <col min="26" max="26" width="10.4285714285714" style="1" customWidth="1"/>
@@ -4180,7 +4180,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AK23" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AK25" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
